--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487927_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487927_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.3765</v>
+        <v>8.0677</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1388</v>
+        <v>6.9181</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2377</v>
+        <v>1.1496</v>
       </c>
       <c r="G2" t="n">
         <v>0.9475</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2801</v>
+        <v>0.9714</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0093</v>
+        <v>0.7887</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2708</v>
+        <v>0.1827</v>
       </c>
       <c r="V2" t="n">
         <v>4.9001</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2867</v>
+        <v>4.3392</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7696</v>
+        <v>4.734</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4828</v>
+        <v>-0.3948</v>
       </c>
       <c r="G3" t="n">
         <v>1.3152</v>
@@ -688,13 +688,13 @@
         <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5904</v>
+        <v>0.4621</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6524</v>
+        <v>0.312</v>
       </c>
       <c r="U3" t="n">
-        <v>0.062</v>
+        <v>0.1501</v>
       </c>
       <c r="V3" t="n">
         <v>1.5213</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4022</v>
+        <v>2.3832</v>
       </c>
       <c r="E4" t="n">
-        <v>1.034</v>
+        <v>0.9268</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3682</v>
+        <v>1.4563</v>
       </c>
       <c r="G4" t="n">
         <v>0.213</v>
@@ -766,13 +766,13 @@
         <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1892</v>
+        <v>0.1701</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3882</v>
+        <v>0.281</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.199</v>
+        <v>-0.1109</v>
       </c>
       <c r="V4" t="n">
         <v>1.1675</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. GARCIA PEREZ</t>
+          <t>P. UNIACKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9038</v>
+        <v>0.8421</v>
       </c>
       <c r="E5" t="n">
-        <v>1.78</v>
+        <v>0.0342</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1237</v>
+        <v>0.8078</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5153</v>
+        <v>0.4739</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5823</v>
+        <v>0.4372</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0669</v>
+        <v>0.0367</v>
       </c>
       <c r="J5" t="n">
-        <v>1.344</v>
+        <v>0.0576</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3048</v>
+        <v>0.0576</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0392</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1713</v>
+        <v>0.4164</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2775</v>
+        <v>0.3796</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1061</v>
+        <v>0.0367</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9306</v>
+        <v>0.16</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2051</v>
+        <v>-0.0233</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7255</v>
+        <v>0.1833</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.1665</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.769</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. UNIACKE</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7349</v>
+        <v>0.5788</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.07290000000000001</v>
+        <v>3.7928</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8078</v>
+        <v>-3.214</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4739</v>
+        <v>2.3639</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4372</v>
+        <v>0.3008</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0367</v>
+        <v>2.0631</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0576</v>
+        <v>4.3195</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0576</v>
+        <v>1.938</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.3815</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4164</v>
+        <v>-1.9556</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3796</v>
+        <v>-1.6372</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0367</v>
+        <v>-0.3184</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0529</v>
+        <v>-0.115</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1305</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1833</v>
+        <v>0.4117</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.9188</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. RUIZ CRESPO</t>
+          <t>L. GARCIA PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3053</v>
+        <v>0.3639</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3053</v>
+        <v>-0.0231</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2857</v>
+        <v>1.5153</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1429</v>
+        <v>1.5823</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1429</v>
+        <v>-0.0669</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.344</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.3048</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0392</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2857</v>
+        <v>0.1713</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1429</v>
+        <v>0.2775</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1429</v>
+        <v>-0.1061</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0196</v>
+        <v>1.3908</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0196</v>
+        <v>0.5787</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-3.1665</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-1.769</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>J. RUIZ CRESPO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1015</v>
+        <v>0.3347</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4061</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.5076</v>
+        <v>0.3347</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3639</v>
+        <v>0.2857</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3008</v>
+        <v>0.1429</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0631</v>
+        <v>0.1429</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3195</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.938</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3815</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9556</v>
+        <v>0.2857</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6372</v>
+        <v>0.1429</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3184</v>
+        <v>0.1429</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7953</v>
+        <v>0.0489</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9134</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1181</v>
+        <v>0.0489</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.9188</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3853</v>
+        <v>-0.0191</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8894</v>
+        <v>1.4904</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2746</v>
+        <v>-1.5095</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4461</v>
@@ -1156,13 +1156,13 @@
         <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1285</v>
+        <v>0.2376</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9134</v>
+        <v>-0.3124</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7849</v>
+        <v>0.55</v>
       </c>
       <c r="V9" t="n">
         <v>1.9813</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4606</v>
+        <v>-0.6869</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6495</v>
+        <v>-1.0364</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1101</v>
+        <v>0.3495</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4533</v>
+        <v>-4.6838</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5821</v>
+        <v>1.0043</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8711</v>
+        <v>-5.688</v>
       </c>
       <c r="J10" t="n">
-        <v>0.196</v>
+        <v>-2.4953</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2834</v>
+        <v>2.2702</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-4.7655</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6493</v>
+        <v>-2.1884</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8655</v>
+        <v>-1.2659</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.9225</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8064</v>
+        <v>1.0406</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4534</v>
+        <v>-0.2924</v>
       </c>
       <c r="U10" t="n">
-        <v>0.353</v>
+        <v>1.3329</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.23</v>
+        <v>1.2914</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.23</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9459</v>
+        <v>-0.6955</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5303</v>
+        <v>0.6495</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5844</v>
+        <v>-1.3449</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.6838</v>
+        <v>-1.4533</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0043</v>
+        <v>-0.5821</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.688</v>
+        <v>-0.8711</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4953</v>
+        <v>0.196</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2702</v>
+        <v>0.2834</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.7655</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1884</v>
+        <v>-1.6493</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2659</v>
+        <v>-0.8655</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9225</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7816</v>
+        <v>0.5715</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7862</v>
+        <v>0.4534</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5678</v>
+        <v>0.1181</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2914</v>
+        <v>-0.23</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4599</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5045</v>
+        <v>-1.5823</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07820000000000001</v>
+        <v>-0.029</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5826</v>
+        <v>-1.5533</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3784</v>
@@ -1390,13 +1390,13 @@
         <v>1.4568</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4358</v>
+        <v>0.358</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2643</v>
+        <v>-0.3714</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.7294</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9376</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3874</v>
+        <v>-2.3754</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.452</v>
+        <v>-2.8509</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0645</v>
+        <v>0.4756</v>
       </c>
       <c r="G13" t="n">
         <v>-0.09180000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.717</v>
+        <v>0.295</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3049</v>
+        <v>-0.7038</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5878</v>
+        <v>0.9989</v>
       </c>
       <c r="V13" t="n">
         <v>1.1675</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.2242</v>
+        <v>11.5504</v>
       </c>
       <c r="E14" t="n">
-        <v>14.6904</v>
+        <v>15.0165</v>
       </c>
       <c r="F14" t="n">
         <v>-3.4661</v>
@@ -1513,7 +1513,7 @@
         <v>-1.9389</v>
       </c>
       <c r="H14" t="n">
-        <v>7.879000000000002</v>
+        <v>7.879</v>
       </c>
       <c r="I14" t="n">
         <v>-9.817400000000001</v>
@@ -1525,16 +1525,16 @@
         <v>13.2698</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.674200000000001</v>
+        <v>-4.6742</v>
       </c>
       <c r="M14" t="n">
         <v>-10.5341</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.390700000000001</v>
+        <v>-5.390699999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.1433</v>
+        <v>-5.143299999999999</v>
       </c>
       <c r="P14" t="n">
         <v>3.1217</v>
@@ -1546,16 +1546,16 @@
         <v>11.4464</v>
       </c>
       <c r="S14" t="n">
-        <v>5.265000000000001</v>
+        <v>5.591</v>
       </c>
       <c r="T14" t="n">
-        <v>0.09089999999999998</v>
+        <v>0.4171000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>5.1739</v>
+        <v>5.1738</v>
       </c>
       <c r="V14" t="n">
-        <v>4.776199999999999</v>
+        <v>4.776200000000001</v>
       </c>
       <c r="W14" t="n">
         <v>14.3287</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0874</v>
+        <v>4.4486</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0718</v>
+        <v>4.2861</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0156</v>
+        <v>0.1624</v>
       </c>
       <c r="G15" t="n">
         <v>5.8817</v>
@@ -1624,13 +1624,13 @@
         <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2937</v>
+        <v>-0.9326</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4354</v>
+        <v>-1.221</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1416</v>
+        <v>0.2884</v>
       </c>
       <c r="V15" t="n">
         <v>0.1238</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1858</v>
+        <v>0.8541</v>
       </c>
       <c r="E16" t="n">
-        <v>2.736</v>
+        <v>2.5217</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5502</v>
+        <v>-1.6676</v>
       </c>
       <c r="G16" t="n">
         <v>0.5717</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2603</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2577</v>
+        <v>0.0434</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0026</v>
+        <v>-0.1148</v>
       </c>
       <c r="V16" t="n">
         <v>0.3538</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.3356</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0153</v>
+        <v>0.3368</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6136</v>
+        <v>-0.6723</v>
       </c>
       <c r="G18" t="n">
         <v>0.143</v>
@@ -1858,13 +1858,13 @@
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.646</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9134</v>
+        <v>-0.5919</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0046</v>
+        <v>-0.0541</v>
       </c>
       <c r="V18" t="n">
         <v>0.5838</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ISERN MAZA</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8126</v>
+        <v>-0.7244</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1642</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.9768</v>
+        <v>-0.2219</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0104</v>
+        <v>-1.4122</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1048</v>
+        <v>-2.2025</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1151</v>
+        <v>0.7903</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5538</v>
+        <v>-0.8405</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7285</v>
+        <v>-0.949</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1747</v>
+        <v>0.1086</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5434</v>
+        <v>-0.5717</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8332</v>
+        <v>-1.2535</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2898</v>
+        <v>0.6817</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7418</v>
+        <v>-0.9365</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3948</v>
+        <v>-0.8296</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.347</v>
+        <v>-0.107</v>
       </c>
       <c r="V19" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.1675</v>
       </c>
-      <c r="W19" t="n">
-        <v>4.0863</v>
-      </c>
       <c r="X19" t="n">
-        <v>-2.9188</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GARCIA-ABRIL GUERRERO</t>
+          <t>P. ISERN MAZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9747</v>
+        <v>-0.8023</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6607</v>
+        <v>3.057</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.314</v>
+        <v>-3.8593</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6713</v>
+        <v>0.0104</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9571</v>
+        <v>-0.1048</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2857</v>
+        <v>0.1151</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1077</v>
+        <v>1.5538</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5373</v>
+        <v>1.7285</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.645</v>
+        <v>-0.1747</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5636</v>
+        <v>-1.5434</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4943</v>
+        <v>-1.8332</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9307</v>
+        <v>0.2898</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4064</v>
+        <v>-0.7315</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7829</v>
+        <v>-0.5019</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3765</v>
+        <v>-0.2296</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9376</v>
+        <v>1.1675</v>
       </c>
       <c r="W20" t="n">
-        <v>0.23</v>
+        <v>4.0863</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1675</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>J. GARCIA-ABRIL GUERRERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9974</v>
+        <v>-1.0349</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7168</v>
+        <v>-0.3392</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2806</v>
+        <v>-0.6957</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4122</v>
+        <v>-0.6713</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2025</v>
+        <v>-0.9571</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7903</v>
+        <v>0.2857</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8405</v>
+        <v>-0.1077</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.949</v>
+        <v>0.5373</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1086</v>
+        <v>-0.645</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5717</v>
+        <v>-0.5636</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2535</v>
+        <v>-1.4943</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6817</v>
+        <v>0.9307</v>
       </c>
       <c r="P21" t="n">
         <v>1.0406</v>
@@ -2092,22 +2092,22 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2096</v>
+        <v>-0.4666</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0439</v>
+        <v>-0.4615</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1657</v>
+        <v>-0.0052</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5838</v>
+        <v>-0.9376</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8505</v>
+        <v>-2.3966</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2071</v>
+        <v>-0.2215</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0576</v>
+        <v>-2.1751</v>
       </c>
       <c r="G22" t="n">
         <v>1.6874</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0646</v>
+        <v>-0.4815</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1239</v>
+        <v>-0.3047</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0593</v>
+        <v>-0.1767</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5213</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2959</v>
+        <v>-4.9579</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7779</v>
+        <v>-1.528</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.518</v>
+        <v>-3.4299</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5287</v>
@@ -2248,13 +2248,13 @@
         <v>1.4568</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3816</v>
+        <v>-0.2804</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0066</v>
+        <v>-0.7567</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3882</v>
+        <v>0.4763</v>
       </c>
       <c r="V23" t="n">
         <v>-2.565</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2538</v>
+        <v>-6.561</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5728</v>
+        <v>-4.1442</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.681</v>
+        <v>-2.4168</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0289</v>
@@ -2326,13 +2326,13 @@
         <v>0.8325</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4112</v>
+        <v>-0.7183</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9786</v>
+        <v>-0.55</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4325</v>
+        <v>-0.1683</v>
       </c>
       <c r="V24" t="n">
         <v>-2.565</v>
@@ -2362,7 +2362,7 @@
         <v>-11.2243</v>
       </c>
       <c r="E25" t="n">
-        <v>3.4662</v>
+        <v>3.466200000000001</v>
       </c>
       <c r="F25" t="n">
         <v>-14.6905</v>
@@ -2404,16 +2404,16 @@
         <v>8.3248</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.265000000000001</v>
+        <v>-5.2648</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.174</v>
+        <v>-5.1739</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.09099999999999997</v>
+        <v>-0.09100000000000003</v>
       </c>
       <c r="V25" t="n">
-        <v>-4.7762</v>
+        <v>-4.776199999999999</v>
       </c>
       <c r="W25" t="n">
         <v>9.5525</v>
